--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484872_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484872_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6023</v>
+        <v>3.4667</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3621</v>
+        <v>7.2001</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.7598</v>
+        <v>-3.7333</v>
       </c>
       <c r="G2" t="n">
         <v>2.3208</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9985</v>
+        <v>1.8629</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8814</v>
+        <v>1.7193</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1171</v>
+        <v>0.1435</v>
       </c>
       <c r="V2" t="n">
         <v>-2.2265</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9138</v>
+        <v>1.9869</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1127</v>
+        <v>0.1329</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8011</v>
+        <v>1.854</v>
       </c>
       <c r="G3" t="n">
         <v>0.5286</v>
@@ -688,13 +688,13 @@
         <v>0.3774</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.628</v>
       </c>
       <c r="T3" t="n">
-        <v>0.238</v>
+        <v>0.2582</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3169</v>
+        <v>0.3698</v>
       </c>
       <c r="V3" t="n">
         <v>0.6415999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.626</v>
+        <v>0.7763</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8678</v>
+        <v>-0.7703</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4938</v>
+        <v>1.5467</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3695</v>
@@ -844,13 +844,13 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7783</v>
+        <v>-0.628</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2816</v>
+        <v>-0.1842</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4967</v>
+        <v>-0.4438</v>
       </c>
       <c r="V5" t="n">
         <v>0.6415999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>J. MARTINEZ MUNOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6697</v>
+        <v>-0.2811</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6425</v>
+        <v>-1.9927</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3121</v>
+        <v>1.7116</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2456</v>
+        <v>-5.5725</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5314</v>
+        <v>-2.0809</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7143</v>
+        <v>-3.4915</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2058</v>
+        <v>-3.7419</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2058</v>
+        <v>-1.9166</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.8253</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0398</v>
+        <v>-1.8306</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3256</v>
+        <v>-0.1643</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7143</v>
+        <v>-1.6662</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>2.4531</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0664</v>
+        <v>1.1785</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6031</v>
+        <v>0.731</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4633</v>
+        <v>0.4474</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2452</v>
+        <v>4.679</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>4.0374</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4904</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1711</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6385</v>
+        <v>1.6425</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5326</v>
+        <v>-2.5502</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5207</v>
+        <v>-1.2456</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5682</v>
+        <v>-0.5314</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9525</v>
+        <v>-0.7143</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5261</v>
+        <v>-0.2058</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.2058</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0054</v>
+        <v>-1.0398</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3083</v>
+        <v>-0.3256</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.303</v>
+        <v>-0.7143</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0287</v>
+        <v>0.8283</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.6031</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1411</v>
+        <v>0.2252</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUNOZ</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5989</v>
+        <v>-1.0557</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0459</v>
+        <v>-3.3717</v>
       </c>
       <c r="F8" t="n">
-        <v>1.447</v>
+        <v>2.316</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.5725</v>
+        <v>-2.5492</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0809</v>
+        <v>0.4187</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.4915</v>
+        <v>-2.9679</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.7419</v>
+        <v>-1.3574</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9166</v>
+        <v>0.5501</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8253</v>
+        <v>-1.9076</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8306</v>
+        <v>-1.1918</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1643</v>
+        <v>-0.1315</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6662</v>
+        <v>-1.0603</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0192</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1394</v>
+        <v>1.1917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3223</v>
+        <v>0.7219</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1829</v>
+        <v>0.4698</v>
       </c>
       <c r="V8" t="n">
-        <v>4.679</v>
+        <v>0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>4.0374</v>
+        <v>-0.6606</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8876</v>
+        <v>-1.3492</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2301</v>
+        <v>-1.0282</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3425</v>
+        <v>-0.321</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5492</v>
+        <v>-1.5207</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4187</v>
+        <v>-0.5682</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9679</v>
+        <v>-0.9525</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3574</v>
+        <v>-1.5261</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5501</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9076</v>
+        <v>-0.6496</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1918</v>
+        <v>0.0054</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1315</v>
+        <v>0.3083</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0603</v>
+        <v>-0.303</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0757</v>
+        <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3598</v>
+        <v>0.8506</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1365</v>
+        <v>0.4979</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4962</v>
+        <v>0.3527</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6606</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9624</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0599</v>
+        <v>-3.2166</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0679</v>
+        <v>-5.1452</v>
       </c>
       <c r="F10" t="n">
-        <v>2.008</v>
+        <v>1.9286</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8159999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6431</v>
+        <v>0.4864</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1357</v>
+        <v>0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5074</v>
+        <v>0.428</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6226</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0181</v>
+        <v>-3.8501</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6086</v>
+        <v>-1.3348</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4095</v>
+        <v>-2.5153</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5484</v>
@@ -1312,13 +1312,13 @@
         <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>1.606</v>
+        <v>1.774</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0328</v>
+        <v>1.3066</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5732</v>
+        <v>0.4674</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6226</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.621499999999999</v>
+        <v>-7.2784</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.894399999999999</v>
+        <v>-8.3926</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2729</v>
+        <v>1.1142</v>
       </c>
       <c r="G12" t="n">
         <v>-7.3297</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8388</v>
+        <v>0.5042</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3862</v>
+        <v>0.1156</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5474</v>
+        <v>0.3887</v>
       </c>
       <c r="V12" t="n">
         <v>0.3018</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.6338</v>
+        <v>-10.4581</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.985</v>
+        <v>-11.8091</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3513</v>
+        <v>1.351300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-17.8513</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5904</v>
+        <v>-2.590400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-15.2608</v>
@@ -1468,19 +1468,19 @@
         <v>15.096</v>
       </c>
       <c r="S13" t="n">
-        <v>7.500900000000001</v>
+        <v>8.676600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.651999999999999</v>
+        <v>5.827799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8488</v>
+        <v>2.8487</v>
       </c>
       <c r="V13" t="n">
         <v>0.6036999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7157</v>
+        <v>6.715700000000002</v>
       </c>
       <c r="X13" t="n">
         <v>-6.111999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.692</v>
+        <v>5.4967</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0379</v>
+        <v>6.1353</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3459</v>
+        <v>-0.6387</v>
       </c>
       <c r="G14" t="n">
         <v>8.428100000000001</v>
@@ -1546,13 +1546,13 @@
         <v>3.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.359</v>
+        <v>-1.5544</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6997</v>
+        <v>-0.6022</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6594</v>
+        <v>-0.9522</v>
       </c>
       <c r="V14" t="n">
         <v>-3.4528</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0796</v>
+        <v>3.7399</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4286</v>
+        <v>-0.1363</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5083</v>
+        <v>3.8763</v>
       </c>
       <c r="G15" t="n">
         <v>1.1181</v>
@@ -1624,13 +1624,13 @@
         <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3973</v>
+        <v>-0.737</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7272</v>
+        <v>-0.4349</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6701</v>
+        <v>-0.3021</v>
       </c>
       <c r="V15" t="n">
         <v>1.2832</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0507</v>
+        <v>3.1118</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6328</v>
+        <v>0.4725</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4179</v>
+        <v>2.6393</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6672</v>
+        <v>1.3825</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9698</v>
+        <v>0.9908</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6974</v>
+        <v>0.3917</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1922</v>
+        <v>-0.1107</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7115</v>
+        <v>0.4069</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4807</v>
+        <v>-0.5177</v>
       </c>
       <c r="M16" t="n">
-        <v>0.475</v>
+        <v>1.4932</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2583</v>
+        <v>0.5838</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2167</v>
+        <v>0.9094</v>
       </c>
       <c r="P16" t="n">
         <v>-1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8305</v>
+        <v>-3.0192</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3521</v>
+        <v>-0.1949</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6343</v>
+        <v>-0.1332</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2823</v>
+        <v>-0.0617</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2452</v>
+        <v>3.4338</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9054</v>
+        <v>3.7356</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3398</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6812</v>
+        <v>2.8284</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2776</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4036</v>
+        <v>2.0981</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3825</v>
+        <v>3.6672</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9908</v>
+        <v>1.9698</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3917</v>
+        <v>1.6974</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1107</v>
+        <v>3.1922</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4069</v>
+        <v>1.7115</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5177</v>
+        <v>1.4807</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4932</v>
+        <v>0.475</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5838</v>
+        <v>0.2583</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9094</v>
+        <v>0.2167</v>
       </c>
       <c r="P17" t="n">
         <v>-1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0192</v>
+        <v>-2.8305</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.5744</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3281</v>
+        <v>-0.5369</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2974</v>
+        <v>-0.0375</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4338</v>
+        <v>1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7356</v>
+        <v>0.9054</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MUÑOZ PALENCIA</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5509</v>
+        <v>1.7884</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5509</v>
+        <v>0.7897</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.9987</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5509</v>
+        <v>3.4226</v>
       </c>
       <c r="H18" t="n">
-        <v>0.317</v>
+        <v>0.3319</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2339</v>
+        <v>3.0907</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5509</v>
+        <v>2.3384</v>
       </c>
       <c r="K18" t="n">
-        <v>0.317</v>
+        <v>0.2222</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2339</v>
+        <v>2.1161</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.0842</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.1096</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.9746</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.8305</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-1.4646</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.7464</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>J. MUÑOZ PALENCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9545</v>
+        <v>1.5509</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9458</v>
+        <v>1.5509</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9004</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0633</v>
+        <v>1.5509</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4249</v>
+        <v>0.317</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3617</v>
+        <v>1.2339</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4784</v>
+        <v>1.5509</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6018</v>
+        <v>0.317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1234</v>
+        <v>1.2339</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4152</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1769</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2383</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7536</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6647999999999999</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0888</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.867</v>
+        <v>0.3123</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2051</v>
+        <v>-1.5304</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6618000000000001</v>
+        <v>1.8427</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4226</v>
+        <v>-0.0633</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3319</v>
+        <v>-0.4249</v>
       </c>
       <c r="I20" t="n">
-        <v>3.0907</v>
+        <v>0.3617</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3384</v>
+        <v>-0.4784</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2222</v>
+        <v>-0.6018</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1161</v>
+        <v>0.1234</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0842</v>
+        <v>0.4152</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1096</v>
+        <v>0.1769</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9746</v>
+        <v>0.2383</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.3774</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.1322</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.7548</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.0757</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.8305</v>
-      </c>
       <c r="S20" t="n">
-        <v>-2.386</v>
+        <v>0.1114</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3028</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0833</v>
+        <v>0.0312</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9244</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1696</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="G21" t="n">
         <v>0.1299</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. STANESCU</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2963</v>
+        <v>-0.2992</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6496</v>
+        <v>-3.5455</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3533</v>
+        <v>3.2464</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5196</v>
+        <v>-0.8616</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6496</v>
+        <v>-0.378</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1299</v>
+        <v>-0.4836</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6496</v>
+        <v>-1.7517</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6496</v>
+        <v>-0.5534</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1299</v>
+        <v>0.8901</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.1753</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1299</v>
+        <v>0.7148</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2644</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2234</v>
+        <v>-0.8335</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.7367</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2234</v>
+        <v>-0.0969</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2072</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>R. STANESCU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8958</v>
+        <v>-0.4021</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9353</v>
+        <v>-0.6496</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0394</v>
+        <v>0.2475</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8616</v>
+        <v>-0.5196</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.378</v>
+        <v>-0.6496</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4836</v>
+        <v>0.1299</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7517</v>
+        <v>-0.6496</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5534</v>
+        <v>-0.6496</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1984</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8901</v>
+        <v>0.1299</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1753</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7148</v>
+        <v>0.1299</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2644</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4302</v>
+        <v>0.1176</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1264</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3038</v>
+        <v>0.1176</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2072</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8321</v>
+        <v>-2.3126</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8921</v>
+        <v>0.0411</v>
       </c>
       <c r="F24" t="n">
-        <v>1.06</v>
+        <v>-2.3537</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8829</v>
+        <v>0.4794</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9391</v>
+        <v>0.0485</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0562</v>
+        <v>0.4309</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8005</v>
+        <v>0.0411</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.839</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9616</v>
+        <v>0.0411</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9176</v>
+        <v>0.4383</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1001</v>
+        <v>0.0485</v>
       </c>
       <c r="O24" t="n">
-        <v>1.0177</v>
+        <v>0.3897</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4091</v>
+        <v>-0.3016</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3049</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8958</v>
+        <v>-0.3016</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.547</v>
+        <v>-2.4904</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2262</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3655</v>
+        <v>-2.406</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0411</v>
+        <v>-3.9639</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4066</v>
+        <v>1.5579</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4794</v>
+        <v>-0.8829</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0485</v>
+        <v>-0.9391</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4309</v>
+        <v>0.0562</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0411</v>
+        <v>-1.8005</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-0.839</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0411</v>
+        <v>-0.9616</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4383</v>
+        <v>0.9176</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0485</v>
+        <v>-0.1001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3897</v>
+        <v>1.0177</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3545</v>
+        <v>-0.1648</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.2331</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3545</v>
+        <v>-0.3979</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.4904</v>
+        <v>-1.547</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.4904</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11.6337</v>
+        <v>13.5825</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1060000000000009</v>
+        <v>-0.1059000000000019</v>
       </c>
       <c r="F26" t="n">
-        <v>11.7397</v>
+        <v>13.6885</v>
       </c>
       <c r="G26" t="n">
         <v>17.8513</v>
@@ -2470,7 +2470,7 @@
         <v>1.1976</v>
       </c>
       <c r="O26" t="n">
-        <v>6.172100000000001</v>
+        <v>6.1721</v>
       </c>
       <c r="P26" t="n">
         <v>1.887</v>
@@ -2482,13 +2482,13 @@
         <v>16.983</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.500900000000001</v>
+        <v>-5.552099999999998</v>
       </c>
       <c r="T26" t="n">
         <v>-2.8488</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.6522</v>
+        <v>-2.7034</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6035999999999995</v>
@@ -2497,7 +2497,7 @@
         <v>7.357200000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.9608</v>
+        <v>-7.960800000000001</v>
       </c>
     </row>
   </sheetData>
